--- a/diseases/d134/2026-2029.xlsx
+++ b/diseases/d134/2026-2029.xlsx
@@ -5686,6 +5686,151 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>aseptic-meningitis</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>无菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>18</v>
+      </c>
+      <c r="O36" t="n">
+        <v>18</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.01470255133618379</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP36" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR36" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS36" t="inlineStr"/>
+      <c r="AT36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV36" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA36" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB36" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC36" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5719,7 +5864,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-30</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5947,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
@@ -5812,7 +5957,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="11">
@@ -5864,7 +6009,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>597</v>
+        <v>615</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d134/2026-2029.xlsx
+++ b/diseases/d134/2026-2029.xlsx
@@ -5831,6 +5831,151 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>aseptic-meningitis</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>无菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N37" t="n">
+        <v>22</v>
+      </c>
+      <c r="O37" t="n">
+        <v>22</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.01796978496644686</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP37" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR37" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS37" t="inlineStr"/>
+      <c r="AT37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV37" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA37" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB37" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC37" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5864,7 +6009,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -5947,7 +6092,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
@@ -5957,7 +6102,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
@@ -6009,7 +6154,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>615</v>
+        <v>637</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d134/2026-2029.xlsx
+++ b/diseases/d134/2026-2029.xlsx
@@ -5976,6 +5976,151 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>aseptic-meningitis</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>无菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>24</v>
+      </c>
+      <c r="O38" t="n">
+        <v>24</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.01960340178157839</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP38" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR38" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS38" t="inlineStr"/>
+      <c r="AT38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV38" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA38" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB38" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC38" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6009,7 +6154,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -6092,7 +6237,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
@@ -6102,7 +6247,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11">
@@ -6154,7 +6299,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>637</v>
+        <v>661</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d134/2026-2029.xlsx
+++ b/diseases/d134/2026-2029.xlsx
@@ -6121,6 +6121,151 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>aseptic-meningitis</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>无菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>22</v>
+      </c>
+      <c r="O39" t="n">
+        <v>22</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.01796978496644686</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP39" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR39" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr"/>
+      <c r="AT39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV39" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA39" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB39" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC39" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6154,7 +6299,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-20</t>
         </is>
       </c>
     </row>
@@ -6237,7 +6382,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
@@ -6247,7 +6392,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11">
@@ -6299,7 +6444,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>661</v>
+        <v>683</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d134/2026-2029.xlsx
+++ b/diseases/d134/2026-2029.xlsx
@@ -6266,6 +6266,151 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>aseptic-meningitis</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>无菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N40" t="n">
+        <v>24</v>
+      </c>
+      <c r="O40" t="n">
+        <v>24</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.01960340178157839</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP40" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR40" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr"/>
+      <c r="AT40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV40" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA40" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB40" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC40" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6299,7 +6444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-27</t>
         </is>
       </c>
     </row>
@@ -6382,7 +6527,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
@@ -6392,7 +6537,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11">
@@ -6444,7 +6589,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>683</v>
+        <v>707</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d134/2026-2029.xlsx
+++ b/diseases/d134/2026-2029.xlsx
@@ -6411,6 +6411,151 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>aseptic-meningitis</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>无菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N41" t="n">
+        <v>25</v>
+      </c>
+      <c r="O41" t="n">
+        <v>25</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.02042021018914416</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP41" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR41" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS41" t="inlineStr"/>
+      <c r="AT41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV41" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA41" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB41" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC41" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6444,7 +6589,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -6527,7 +6672,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10">
@@ -6537,7 +6682,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
@@ -6589,7 +6734,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>707</v>
+        <v>732</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d134/2026-2029.xlsx
+++ b/diseases/d134/2026-2029.xlsx
@@ -80508,6 +80508,2886 @@
         </is>
       </c>
     </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>aseptic-meningitis</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>JP-03</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>Iwate, Japan</t>
+        </is>
+      </c>
+      <c r="H555" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="I555" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="J555" t="inlineStr">
+        <is>
+          <t>无菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L555" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="M555" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N555" t="n">
+        <v>1</v>
+      </c>
+      <c r="O555" t="n">
+        <v>1</v>
+      </c>
+      <c r="P555" t="n">
+        <v>1</v>
+      </c>
+      <c r="U555" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AA555" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO555" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP555" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS555" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AT555" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV555" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW555" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX555" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY555" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ555" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA555" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB555" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC555" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>aseptic-meningitis</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>JP-11</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>Saitama, Japan</t>
+        </is>
+      </c>
+      <c r="H556" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="I556" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="J556" t="inlineStr">
+        <is>
+          <t>无菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K556" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L556" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="M556" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N556" t="n">
+        <v>2</v>
+      </c>
+      <c r="O556" t="n">
+        <v>2</v>
+      </c>
+      <c r="P556" t="n">
+        <v>2</v>
+      </c>
+      <c r="U556" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AA556" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO556" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP556" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS556" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AT556" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV556" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW556" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX556" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY556" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ556" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA556" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB556" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC556" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>aseptic-meningitis</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>JP-12</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>Chiba, Japan</t>
+        </is>
+      </c>
+      <c r="H557" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="I557" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="J557" t="inlineStr">
+        <is>
+          <t>无菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L557" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="M557" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N557" t="n">
+        <v>1</v>
+      </c>
+      <c r="O557" t="n">
+        <v>1</v>
+      </c>
+      <c r="P557" t="n">
+        <v>1</v>
+      </c>
+      <c r="U557" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AA557" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO557" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP557" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS557" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AT557" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV557" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW557" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX557" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY557" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ557" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA557" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB557" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC557" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>aseptic-meningitis</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>JP-13</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>Tokyo, Japan</t>
+        </is>
+      </c>
+      <c r="H558" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="I558" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="J558" t="inlineStr">
+        <is>
+          <t>无菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L558" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="M558" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N558" t="n">
+        <v>3</v>
+      </c>
+      <c r="O558" t="n">
+        <v>3</v>
+      </c>
+      <c r="P558" t="n">
+        <v>3</v>
+      </c>
+      <c r="U558" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AA558" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO558" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP558" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS558" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AT558" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV558" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW558" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX558" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY558" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ558" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA558" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB558" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC558" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>aseptic-meningitis</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>JP-15</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>Niigata, Japan</t>
+        </is>
+      </c>
+      <c r="H559" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="I559" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="J559" t="inlineStr">
+        <is>
+          <t>无菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L559" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="M559" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N559" t="n">
+        <v>3</v>
+      </c>
+      <c r="O559" t="n">
+        <v>3</v>
+      </c>
+      <c r="P559" t="n">
+        <v>3</v>
+      </c>
+      <c r="U559" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AA559" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO559" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP559" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS559" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AT559" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV559" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW559" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX559" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY559" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ559" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA559" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB559" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC559" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>aseptic-meningitis</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>JP-19</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>Yamanashi, Japan</t>
+        </is>
+      </c>
+      <c r="H560" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="I560" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="J560" t="inlineStr">
+        <is>
+          <t>无菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L560" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="M560" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N560" t="n">
+        <v>2</v>
+      </c>
+      <c r="O560" t="n">
+        <v>2</v>
+      </c>
+      <c r="P560" t="n">
+        <v>2</v>
+      </c>
+      <c r="U560" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AA560" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO560" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP560" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS560" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AT560" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV560" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW560" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX560" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY560" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ560" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA560" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB560" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC560" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>aseptic-meningitis</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>JP-21</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>Gifu, Japan</t>
+        </is>
+      </c>
+      <c r="H561" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="I561" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="J561" t="inlineStr">
+        <is>
+          <t>无菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L561" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="M561" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N561" t="n">
+        <v>1</v>
+      </c>
+      <c r="O561" t="n">
+        <v>1</v>
+      </c>
+      <c r="P561" t="n">
+        <v>1</v>
+      </c>
+      <c r="U561" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AA561" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO561" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP561" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS561" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AT561" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV561" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW561" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX561" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY561" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ561" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA561" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB561" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC561" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>aseptic-meningitis</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>JP-22</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>Shizuoka, Japan</t>
+        </is>
+      </c>
+      <c r="H562" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="I562" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="J562" t="inlineStr">
+        <is>
+          <t>无菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L562" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="M562" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N562" t="n">
+        <v>2</v>
+      </c>
+      <c r="O562" t="n">
+        <v>2</v>
+      </c>
+      <c r="P562" t="n">
+        <v>2</v>
+      </c>
+      <c r="U562" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AA562" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO562" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP562" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS562" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AT562" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV562" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW562" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX562" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY562" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ562" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA562" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB562" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC562" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>aseptic-meningitis</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>JP-23</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>Aichi, Japan</t>
+        </is>
+      </c>
+      <c r="H563" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="I563" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="J563" t="inlineStr">
+        <is>
+          <t>无菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L563" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="M563" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N563" t="n">
+        <v>3</v>
+      </c>
+      <c r="O563" t="n">
+        <v>3</v>
+      </c>
+      <c r="P563" t="n">
+        <v>3</v>
+      </c>
+      <c r="U563" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AA563" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO563" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP563" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS563" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AT563" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV563" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW563" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX563" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY563" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ563" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA563" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB563" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC563" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>aseptic-meningitis</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>JP-26</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>Kyoto, Japan</t>
+        </is>
+      </c>
+      <c r="H564" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="I564" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="J564" t="inlineStr">
+        <is>
+          <t>无菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L564" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="M564" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N564" t="n">
+        <v>1</v>
+      </c>
+      <c r="O564" t="n">
+        <v>1</v>
+      </c>
+      <c r="P564" t="n">
+        <v>1</v>
+      </c>
+      <c r="U564" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AA564" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO564" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP564" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS564" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AT564" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV564" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW564" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX564" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY564" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ564" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA564" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB564" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC564" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>aseptic-meningitis</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>JP-28</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>Hyogo, Japan</t>
+        </is>
+      </c>
+      <c r="H565" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="I565" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="J565" t="inlineStr">
+        <is>
+          <t>无菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L565" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="M565" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N565" t="n">
+        <v>3</v>
+      </c>
+      <c r="O565" t="n">
+        <v>3</v>
+      </c>
+      <c r="P565" t="n">
+        <v>3</v>
+      </c>
+      <c r="U565" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AA565" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO565" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP565" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS565" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AT565" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV565" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW565" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX565" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY565" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ565" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA565" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB565" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC565" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>aseptic-meningitis</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>JP-29</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>Nara, Japan</t>
+        </is>
+      </c>
+      <c r="H566" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="I566" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="J566" t="inlineStr">
+        <is>
+          <t>无菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L566" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="M566" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N566" t="n">
+        <v>1</v>
+      </c>
+      <c r="O566" t="n">
+        <v>1</v>
+      </c>
+      <c r="P566" t="n">
+        <v>1</v>
+      </c>
+      <c r="U566" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AA566" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO566" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP566" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS566" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AT566" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV566" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW566" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX566" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY566" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ566" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA566" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB566" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC566" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>aseptic-meningitis</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>JP-33</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>Okayama, Japan</t>
+        </is>
+      </c>
+      <c r="H567" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="J567" t="inlineStr">
+        <is>
+          <t>无菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L567" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="M567" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N567" t="n">
+        <v>2</v>
+      </c>
+      <c r="O567" t="n">
+        <v>2</v>
+      </c>
+      <c r="P567" t="n">
+        <v>2</v>
+      </c>
+      <c r="U567" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AA567" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO567" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP567" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS567" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AT567" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV567" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW567" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX567" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY567" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ567" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA567" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB567" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC567" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>aseptic-meningitis</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>JP-34</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>Hiroshima, Japan</t>
+        </is>
+      </c>
+      <c r="H568" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="I568" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="J568" t="inlineStr">
+        <is>
+          <t>无菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L568" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="M568" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N568" t="n">
+        <v>1</v>
+      </c>
+      <c r="O568" t="n">
+        <v>1</v>
+      </c>
+      <c r="P568" t="n">
+        <v>1</v>
+      </c>
+      <c r="U568" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AA568" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO568" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP568" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS568" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AT568" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV568" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW568" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX568" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY568" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ568" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA568" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB568" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC568" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>aseptic-meningitis</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>JP-37</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>Kagawa, Japan</t>
+        </is>
+      </c>
+      <c r="H569" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="J569" t="inlineStr">
+        <is>
+          <t>无菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L569" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="M569" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N569" t="n">
+        <v>1</v>
+      </c>
+      <c r="O569" t="n">
+        <v>1</v>
+      </c>
+      <c r="P569" t="n">
+        <v>1</v>
+      </c>
+      <c r="U569" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AA569" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO569" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP569" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS569" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AT569" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV569" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW569" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX569" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY569" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ569" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA569" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB569" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC569" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>aseptic-meningitis</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>JP-38</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>Ehime, Japan</t>
+        </is>
+      </c>
+      <c r="H570" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="J570" t="inlineStr">
+        <is>
+          <t>无菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L570" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="M570" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N570" t="n">
+        <v>1</v>
+      </c>
+      <c r="O570" t="n">
+        <v>1</v>
+      </c>
+      <c r="P570" t="n">
+        <v>1</v>
+      </c>
+      <c r="U570" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AA570" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO570" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP570" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS570" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AT570" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV570" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW570" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX570" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY570" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ570" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA570" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB570" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC570" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>aseptic-meningitis</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>JP-40</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>Fukuoka, Japan</t>
+        </is>
+      </c>
+      <c r="H571" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="J571" t="inlineStr">
+        <is>
+          <t>无菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L571" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="M571" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N571" t="n">
+        <v>1</v>
+      </c>
+      <c r="O571" t="n">
+        <v>1</v>
+      </c>
+      <c r="P571" t="n">
+        <v>1</v>
+      </c>
+      <c r="U571" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AA571" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO571" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP571" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS571" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AT571" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV571" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW571" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX571" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY571" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ571" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA571" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB571" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC571" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>aseptic-meningitis</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>JP-41</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>Saga, Japan</t>
+        </is>
+      </c>
+      <c r="H572" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="J572" t="inlineStr">
+        <is>
+          <t>无菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K572" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L572" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="M572" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N572" t="n">
+        <v>1</v>
+      </c>
+      <c r="O572" t="n">
+        <v>1</v>
+      </c>
+      <c r="P572" t="n">
+        <v>1</v>
+      </c>
+      <c r="U572" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AA572" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO572" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP572" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS572" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AT572" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV572" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW572" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX572" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY572" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ572" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA572" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB572" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC572" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>aseptic-meningitis</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>JP-43</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>Kumamoto, Japan</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="J573" t="inlineStr">
+        <is>
+          <t>无菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L573" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="M573" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N573" t="n">
+        <v>1</v>
+      </c>
+      <c r="O573" t="n">
+        <v>1</v>
+      </c>
+      <c r="P573" t="n">
+        <v>1</v>
+      </c>
+      <c r="U573" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AA573" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO573" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP573" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS573" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AT573" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV573" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW573" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX573" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY573" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ573" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA573" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB573" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC573" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>aseptic-meningitis</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>JP-47</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>Okinawa, Japan</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>D134</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>Aseptic meningitis</t>
+        </is>
+      </c>
+      <c r="J574" t="inlineStr">
+        <is>
+          <t>无菌性脑膜炎</t>
+        </is>
+      </c>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L574" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="M574" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N574" t="n">
+        <v>2</v>
+      </c>
+      <c r="O574" t="n">
+        <v>2</v>
+      </c>
+      <c r="P574" t="n">
+        <v>2</v>
+      </c>
+      <c r="U574" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AA574" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO574" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP574" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS574" t="inlineStr">
+        <is>
+          <t>HOLD_JP_83c6dfd7cdf9528b53961c0fce51</t>
+        </is>
+      </c>
+      <c r="AT574" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV574" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW574" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX574" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY574" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ574" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA574" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB574" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC574" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -80541,7 +83421,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -80624,7 +83504,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>553</v>
+        <v>573</v>
       </c>
     </row>
     <row r="10">
@@ -80634,7 +83514,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>553</v>
+        <v>573</v>
       </c>
     </row>
     <row r="11">
@@ -80686,7 +83566,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1495</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="16">
